--- a/Result/profitability/3535.xlsx
+++ b/Result/profitability/3535.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04625000000000001</v>
+        <v>0.10125</v>
       </c>
       <c r="N2" t="n">
-        <v>42.68125000000001</v>
+        <v>42.67625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0.37625</v>
+        <v>0.42375</v>
       </c>
       <c r="N3" t="n">
-        <v>41.34125</v>
+        <v>40.98625000000001</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.56</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6025</v>
+        <v>0.67875</v>
       </c>
       <c r="N4" t="n">
-        <v>40.6575</v>
+        <v>39.89</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8062499999999999</v>
+        <v>0.9725</v>
       </c>
       <c r="N5" t="n">
-        <v>39.5625</v>
+        <v>40.2375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9662499999999999</v>
+        <v>0.98875</v>
       </c>
       <c r="N6" t="n">
-        <v>41.42</v>
+        <v>41.06375000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,10 +1264,10 @@
         <v>-0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9349999999999999</v>
+        <v>0.8675</v>
       </c>
       <c r="N7" t="n">
-        <v>39.53250000000001</v>
+        <v>40.56625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0.82</v>
+        <v>0.7125</v>
       </c>
       <c r="N8" t="n">
-        <v>41.835</v>
+        <v>41.58125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.11</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6825000000000001</v>
+        <v>0.6825</v>
       </c>
       <c r="N9" t="n">
         <v>40.84625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3535</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>203</v>
+      </c>
+      <c r="D75" t="n">
+        <v>114</v>
+      </c>
+      <c r="E75" t="n">
+        <v>90</v>
+      </c>
+      <c r="F75" t="n">
+        <v>44.06</v>
+      </c>
+      <c r="G75" t="n">
+        <v>6</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>10</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.06249999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>44.08875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.8686868686868687</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.030000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04404426122803218</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.108333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.400000000000006</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1396792550439732</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
